--- a/RD-图片内容分析和注释模板-step8.xlsx
+++ b/RD-图片内容分析和注释模板-step8.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
   <si>
     <t>模块ID</t>
   </si>
@@ -59,121 +59,19 @@
     <t>类别平均值</t>
   </si>
   <si>
-    <t>industry_inc_total</t>
+    <t>industry_prof_mix</t>
   </si>
   <si>
     <t>关键年报数据</t>
   </si>
   <si>
-    <t>收入</t>
-  </si>
-  <si>
-    <t>保险服务收入</t>
-  </si>
-  <si>
-    <t>22222223333333333333333333</t>
-  </si>
-  <si>
-    <t>industry_comp_1</t>
-  </si>
-  <si>
-    <t>保险服务收入的构成-非PAA和PAA合同组</t>
+    <t>净利润</t>
+  </si>
+  <si>
+    <t>净利润的贡献-保险服务业绩和投资服务业绩</t>
   </si>
   <si>
     <t>√</t>
-  </si>
-  <si>
-    <t>2222222222222</t>
-  </si>
-  <si>
-    <t>industry_comp_2</t>
-  </si>
-  <si>
-    <t>保险服务收入的构成-非PAA合同组的收入构成</t>
-  </si>
-  <si>
-    <t>4444444444444</t>
-  </si>
-  <si>
-    <t>industry_inv_return</t>
-  </si>
-  <si>
-    <t>净投资回报</t>
-  </si>
-  <si>
-    <t>industry_exp_total</t>
-  </si>
-  <si>
-    <t>费用</t>
-  </si>
-  <si>
-    <t>保险服务费用</t>
-  </si>
-  <si>
-    <t>00000000000000000000</t>
-  </si>
-  <si>
-    <t>industry_exp_1</t>
-  </si>
-  <si>
-    <t>保险服务费用构成</t>
-  </si>
-  <si>
-    <t>？</t>
-  </si>
-  <si>
-    <t>industry_uw_profit</t>
-  </si>
-  <si>
-    <t>承保财务净损益</t>
-  </si>
-  <si>
-    <t>industry_exp_struct</t>
-  </si>
-  <si>
-    <t>业务及管理费（新准则分类）</t>
-  </si>
-  <si>
-    <t>66666666666666</t>
-  </si>
-  <si>
-    <t>industry_perf_total</t>
-  </si>
-  <si>
-    <t>净利润</t>
-  </si>
-  <si>
-    <t>保险服务业绩</t>
-  </si>
-  <si>
-    <t>industry_prof_2025</t>
-  </si>
-  <si>
-    <t>最新年保险服务业绩构成</t>
-  </si>
-  <si>
-    <t>888888888888888</t>
-  </si>
-  <si>
-    <t>industry_prof_2024</t>
-  </si>
-  <si>
-    <t>上一年保险服务业绩构成</t>
-  </si>
-  <si>
-    <t>1000000000000000000</t>
-  </si>
-  <si>
-    <t>industry_inv_profit</t>
-  </si>
-  <si>
-    <t>投资服务业绩</t>
-  </si>
-  <si>
-    <t>industry_prof_mix</t>
-  </si>
-  <si>
-    <t>净利润的贡献-保险服务业绩和投资服务业绩</t>
   </si>
   <si>
     <t>投资利润=净投资回报-承保财务净损益
@@ -196,21 +94,117 @@
     <t>净利润 = 保险利润+投资利润+其他利润（主要包括其他业务收入、营业外收支和所得税费用等）。</t>
   </si>
   <si>
+    <t>industry_inc_total</t>
+  </si>
+  <si>
+    <t>保险服务业绩</t>
+  </si>
+  <si>
+    <t>保险服务收入</t>
+  </si>
+  <si>
+    <t>22222223333333333333333333</t>
+  </si>
+  <si>
+    <t>industry_comp_1</t>
+  </si>
+  <si>
+    <t>保险服务收入的构成-非PAA和PAA合同组</t>
+  </si>
+  <si>
+    <t>2222222222222</t>
+  </si>
+  <si>
+    <t>industry_comp_2</t>
+  </si>
+  <si>
+    <t>保险服务收入的构成-非PAA合同组的收入构成</t>
+  </si>
+  <si>
+    <t>4444444444444</t>
+  </si>
+  <si>
+    <t>industry_exp_total</t>
+  </si>
+  <si>
+    <t>保险服务费用</t>
+  </si>
+  <si>
+    <t>00000000000000000000</t>
+  </si>
+  <si>
+    <t>industry_exp_1</t>
+  </si>
+  <si>
+    <t>保险服务费用构成</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>industry_exp_struct</t>
+  </si>
+  <si>
+    <t>业务及管理费（新准则分类）</t>
+  </si>
+  <si>
+    <t>66666666666666</t>
+  </si>
+  <si>
+    <t>industry_perf_total</t>
+  </si>
+  <si>
+    <t>industry_prof_2025</t>
+  </si>
+  <si>
+    <t>最新年保险服务业绩构成</t>
+  </si>
+  <si>
+    <t>888888888888888</t>
+  </si>
+  <si>
+    <t>industry_prof_2024</t>
+  </si>
+  <si>
+    <t>上一年保险服务业绩构成</t>
+  </si>
+  <si>
+    <t>1000000000000000000</t>
+  </si>
+  <si>
+    <t>industry_inv_return</t>
+  </si>
+  <si>
+    <t>投资服务业绩</t>
+  </si>
+  <si>
+    <t>净投资回报</t>
+  </si>
+  <si>
+    <t>industry_uw_profit</t>
+  </si>
+  <si>
+    <t>承保财务净损益</t>
+  </si>
+  <si>
+    <t>industry_inv_profit</t>
+  </si>
+  <si>
+    <t>industry_oci_profit</t>
+  </si>
+  <si>
+    <t>综合收益</t>
+  </si>
+  <si>
+    <t>其他综合收益</t>
+  </si>
+  <si>
+    <t>333333333333</t>
+  </si>
+  <si>
     <t>industry_total_profit</t>
   </si>
   <si>
-    <t>综合收益</t>
-  </si>
-  <si>
-    <t>industry_oci_profit</t>
-  </si>
-  <si>
-    <t>其他综合收益</t>
-  </si>
-  <si>
-    <t>333333333333</t>
-  </si>
-  <si>
     <t>industry_asset_struct</t>
   </si>
   <si>
@@ -245,6 +239,15 @@
   </si>
   <si>
     <t>上一年摊销前 CSM 变动项占比</t>
+  </si>
+  <si>
+    <t>industry_csm_amort_ratio</t>
+  </si>
+  <si>
+    <t>CSM摊销比率</t>
+  </si>
+  <si>
+    <t>CSM摊销比率=(CSM摊销/摊销前的期末CSM)</t>
   </si>
   <si>
     <t xml:space="preserve">industry_csm_continuity_ratio </t>
@@ -257,15 +260,6 @@
 CSM持续率计算时，新业务CSM的口径与CSM摊销的口径保持一致，为所有业务口径</t>
   </si>
   <si>
-    <t>industry_csm_amort_ratio</t>
-  </si>
-  <si>
-    <t>CSM摊销比率</t>
-  </si>
-  <si>
-    <t>CSM摊销比率=(CSM摊销/摊销前的期末CSM)</t>
-  </si>
-  <si>
     <t>industry_equity_trend</t>
   </si>
   <si>
@@ -299,7 +293,7 @@
     <t>industry_lc_loss_ratio</t>
   </si>
   <si>
-    <t>新业务LC亏损率</t>
+    <t>新业务LC</t>
   </si>
   <si>
     <t>industry_nb_ifrs_margin</t>
@@ -1022,6 +1016,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
@@ -1030,25 +1043,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
@@ -1057,14 +1051,14 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1603,7 +1597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.5309734513274" style="1" customWidth="1"/>
@@ -1649,7 +1643,7 @@
       </c>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" ht="65" customHeight="1" spans="1:20">
+    <row r="2" customFormat="1" ht="70.15" spans="1:20">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -1662,15 +1656,17 @@
       <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="F2" s="10"/>
-      <c r="G2" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" ht="14.65" spans="1:20">
+      <c r="G2" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="14.65" spans="1:20">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>11</v>
@@ -1679,19 +1675,15 @@
         <v>12</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="9" t="s">
         <v>17</v>
       </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" customFormat="1" ht="28.5" spans="1:20">
+      <c r="A4" s="7" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="4" ht="14.65" spans="1:20">
-      <c r="A4" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -1700,47 +1692,49 @@
         <v>12</v>
       </c>
       <c r="D4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="19" t="s">
+    </row>
+    <row r="5" ht="65" customHeight="1" spans="1:20">
+      <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:20">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="19" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="6" ht="14.65" spans="1:20">
       <c r="A6" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="F6" s="10"/>
       <c r="G6" s="19" t="s">
         <v>27</v>
@@ -1754,18 +1748,20 @@
         <v>11</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" ht="14.6" spans="1:20">
+    </row>
+    <row r="8" ht="14.65" spans="1:20">
       <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
@@ -1773,111 +1769,115 @@
         <v>11</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="19" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" ht="14.65" spans="1:20">
       <c r="A9" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="F9" s="10"/>
-      <c r="G9" s="19" t="s">
-        <v>35</v>
-      </c>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" ht="14.65" spans="1:20">
       <c r="A10" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="G10" s="19" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="11" ht="14.65" spans="1:20">
       <c r="A11" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>17</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E11" s="9"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="19" t="s">
-        <v>41</v>
-      </c>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="14.65" spans="1:20">
       <c r="A12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="E12" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="14.65" spans="1:20">
       <c r="A13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" ht="70.15" spans="1:20">
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:20">
       <c r="A14" s="7" t="s">
         <v>47</v>
       </c>
@@ -1885,18 +1885,14 @@
         <v>11</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>17</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E14" s="9"/>
       <c r="F14" s="10"/>
-      <c r="G14" s="10" t="s">
-        <v>49</v>
-      </c>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" ht="14.65" spans="1:20">
       <c r="A15" s="7" t="s">
@@ -1906,16 +1902,16 @@
         <v>11</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" ht="27.75" spans="1:20">
+    <row r="16" ht="14.65" spans="1:20">
       <c r="A16" s="7" t="s">
         <v>52</v>
       </c>
@@ -1923,34 +1919,32 @@
         <v>11</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>53</v>
+        <v>48</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" ht="14.65" spans="1:7">
       <c r="A17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="10">
-        <v>22222222222</v>
+      <c r="G17" s="19" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="18" ht="14.65" spans="1:7">
@@ -1961,48 +1955,48 @@
         <v>11</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
-      <c r="G18" s="19" t="s">
-        <v>59</v>
+      <c r="G18" s="10">
+        <v>22222222222</v>
       </c>
     </row>
     <row r="19" ht="14.65" spans="1:7">
       <c r="A19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>62</v>
-      </c>
       <c r="E19" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" ht="14.65" spans="1:7">
       <c r="A20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
@@ -2010,16 +2004,16 @@
     </row>
     <row r="21" ht="14.65" spans="1:7">
       <c r="A21" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
@@ -2027,169 +2021,169 @@
     </row>
     <row r="22" customFormat="1" ht="14.65" spans="1:7">
       <c r="A22" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
     </row>
     <row r="23" customFormat="1" ht="14.65" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" ht="42.4" spans="1:7">
-      <c r="A24" s="7" t="s">
+    <row r="24" ht="14.65" spans="1:7">
+      <c r="A24" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="13" t="s">
+    </row>
+    <row r="25" ht="42.4" spans="1:7">
+      <c r="A25" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10" t="s">
+      <c r="B25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="25" ht="14.65" spans="1:7">
-      <c r="A25" s="15" t="s">
+      <c r="E25" s="15"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="13" t="s">
+    </row>
+    <row r="26" ht="28.5" spans="1:7">
+      <c r="A26" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="7" t="s">
+      <c r="B26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" ht="27.75" spans="1:7">
-      <c r="A26" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>79</v>
+      <c r="D26" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" ht="14.65" spans="1:7">
       <c r="A27" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="10"/>
       <c r="G27" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="14.65" spans="1:7">
       <c r="A28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
       <c r="G28" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" ht="14.65" spans="1:7">
       <c r="A29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="17"/>
+    </row>
+    <row r="30" ht="70.15" spans="1:7">
+      <c r="A30" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="16" t="s">
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="E29" s="17"/>
-    </row>
-    <row r="30" ht="69.4" spans="1:7">
-      <c r="A30" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
